--- a/checklists/checklist.xlsx
+++ b/checklists/checklist.xlsx
@@ -1461,7 +1461,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="3.6640625" customWidth="1" style="82" min="1" max="1"/>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="66" customHeight="1" s="82">
+    <row r="6" ht="49.5" customHeight="1" s="82">
       <c r="A6" s="19" t="n"/>
       <c r="B6" s="34" t="inlineStr">
         <is>
@@ -1548,12 +1548,12 @@
         </is>
       </c>
       <c r="C6" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/01-Conduct_Search_Engine_Discovery_Reconnaissance_for_Information_Leakage", "Conduct Search Engine Discovery Reconnaissance for Information Leakage")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/01-Conduct_Search_Engine_Discovery_Reconnaissance_for_Information_Leakage", "Realizar Reconocimiento de Descubrimiento de Motores de Búsqueda para Fugas de Información")</f>
         <v/>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>- Identify what sensitive design and configuration information of the application, system, or organization is exposed directly (on the organization's site) or indirectly (via third-party services).</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="F6" s="18" t="n"/>
     </row>
-    <row r="7" ht="33" customHeight="1" s="82">
+    <row r="7" ht="16.5" customHeight="1" s="82">
       <c r="A7" s="19" t="n"/>
       <c r="B7" s="34" t="inlineStr">
         <is>
@@ -1571,12 +1571,12 @@
         </is>
       </c>
       <c r="C7" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/02-Fingerprint_Web_Server", "Fingerprint Web Server")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/02-Fingerprint_Web_Server", "Huella Digital del Servidor Web")</f>
         <v/>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>- Determine the version and type of a running web server to enable further discovery of any known vulnerabilities.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="F7" s="18" t="n"/>
     </row>
-    <row r="8" ht="66" customHeight="1" s="82">
+    <row r="8" ht="33" customHeight="1" s="82">
       <c r="A8" s="19" t="n"/>
       <c r="B8" s="34" t="inlineStr">
         <is>
@@ -1594,13 +1594,12 @@
         </is>
       </c>
       <c r="C8" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/03-Review_Webserver_Metafiles_for_Information_Leakage", "Review Webserver Metafiles for Information Leakage")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/03-Review_Webserver_Metafiles_for_Information_Leakage", "Revisar Metafiles del Servidor Web para Fugas de Información")</f>
         <v/>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>- Identify hidden or obfuscated paths and functionality through the analysis of metadata files.
-- Extract and map other information that could lead to a better understanding of the systems at hand.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -1610,7 +1609,7 @@
       </c>
       <c r="F8" s="18" t="n"/>
     </row>
-    <row r="9" ht="33" customHeight="1" s="82">
+    <row r="9" ht="115.5" customHeight="1" s="82">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="34" t="inlineStr">
         <is>
@@ -1618,12 +1617,15 @@
         </is>
       </c>
       <c r="C9" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/04-Enumerate_Applications_on_Webserver", "Enumerate Applications on Webserver")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/04-Attack_Surface_Identification", "Attack Surface Identification")</f>
         <v/>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>- Enumerate the applications within the scope that exist on a web server.</t>
+          <t>- Enumerate all web applications within scope.
+- Identify DNS names, domains, and virtual hosts associated with the target.
+- Discover additional domains and subdomains using passive and active DNS techniques.
+- Analyze digital certificates and Certificate Transparency logs for additional hostnames.</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -1633,7 +1635,7 @@
       </c>
       <c r="F9" s="18" t="n"/>
     </row>
-    <row r="10" ht="115.5" customHeight="1" s="82">
+    <row r="10" ht="33" customHeight="1" s="82">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="34" t="inlineStr">
         <is>
@@ -1641,14 +1643,12 @@
         </is>
       </c>
       <c r="C10" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/05-Review_Web_Page_Content_for_Information_Leakage", "Review Web Page Content for Information Leakage")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/05-Review_Web_Page_Content_for_Information_Leakage", "Revisar Contenido de Página Web para Fugas de Información")</f>
         <v/>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>- Review web page comments, metadata, and redirect bodies to find any information leakage.
-- Gather JavaScript files and review the JS code to better understand the application and to find any information leakage.
-- Identify if source map files or other frontend debug files exist.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
@@ -1666,12 +1666,12 @@
         </is>
       </c>
       <c r="C11" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/06-Identify_Application_Entry_Points", "Identify Application Entry Points")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/06-Identify_Application_Entry_Points", "Identificar Puntos de Entrada de la Aplicación")</f>
         <v/>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>- Identify possible entry and injection points through request and response analysis.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
@@ -1689,12 +1689,12 @@
         </is>
       </c>
       <c r="C12" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/07-Map_Execution_Paths_Through_Application", "Map Execution Paths Through Application")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/07-Map_Execution_Paths_Through_Application", "Mapear Rutas de Ejecución a Través de la Aplicación")</f>
         <v/>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>- Map the target application and understand the principal workflows.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="F12" s="18" t="n"/>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="82">
+    <row r="13" ht="33" customHeight="1" s="82">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="34" t="inlineStr">
         <is>
@@ -1712,12 +1712,12 @@
         </is>
       </c>
       <c r="C13" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/08-Fingerprint_Web_Application_Framework", "Fingerprint Web Application Framework")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/08-Fingerprint_Web_Application_Framework", "Huella Digital del Framework de Aplicación Web")</f>
         <v/>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>- Fingerprint the components used by the web applications.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C14" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/09-Fingerprint_Web_Application", "Fingerprint Web Application")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/09-Fingerprint_Web_Application", "Huella Digital de la Aplicación Web")</f>
         <v/>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F14" s="18" t="n"/>
     </row>
-    <row r="15" ht="33" customHeight="1" s="82">
+    <row r="15" ht="16.5" customHeight="1" s="82">
       <c r="A15" s="19" t="n"/>
       <c r="B15" s="34" t="inlineStr">
         <is>
@@ -1758,12 +1758,12 @@
         </is>
       </c>
       <c r="C15" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/10-Map_Application_Architecture", "Map Application Architecture")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/10-Map_Application_Architecture", "Mapear Arquitectura de la Aplicación")</f>
         <v/>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>- Understand the architecture of the application and the technologies in use.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="82.5" customHeight="1" s="82">
+    <row r="18" ht="33" customHeight="1" s="82">
       <c r="A18" s="19" t="n"/>
       <c r="B18" s="34" t="inlineStr">
         <is>
@@ -1817,13 +1817,12 @@
         </is>
       </c>
       <c r="C18" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/01-Test_Network_Infrastructure_Configuration", "Test Network Infrastructure Configuration")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/01-Test_Network_Infrastructure_Configuration", "Probar Configuración de Infraestructura de Red")</f>
         <v/>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>- Review the applications' configurations set across the network and validate that they are not vulnerable.
-- Validate that used frameworks and systems are secure and not susceptible to known vulnerabilities due to unmaintained software or default settings and credentials.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
@@ -1833,7 +1832,7 @@
       </c>
       <c r="F18" s="18" t="n"/>
     </row>
-    <row r="19" ht="82.5" customHeight="1" s="82">
+    <row r="19" ht="33" customHeight="1" s="82">
       <c r="A19" s="19" t="n"/>
       <c r="B19" s="34" t="inlineStr">
         <is>
@@ -1841,14 +1840,12 @@
         </is>
       </c>
       <c r="C19" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/02-Test_Application_Platform_Configuration", "Test Application Platform Configuration")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/02-Test_Application_Platform_Configuration", "Probar Configuración de Plataforma de Aplicación")</f>
         <v/>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>- Ensure that default and known files have been removed.
-- Validate that no debugging code or extensions are left in the production environments.
-- Review the logging mechanisms set in place for the application.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E19" s="18" t="inlineStr">
@@ -1858,7 +1855,7 @@
       </c>
       <c r="F19" s="18" t="n"/>
     </row>
-    <row r="20" ht="66" customHeight="1" s="82">
+    <row r="20" ht="33" customHeight="1" s="82">
       <c r="A20" s="19" t="n"/>
       <c r="B20" s="34" t="inlineStr">
         <is>
@@ -1866,13 +1863,12 @@
         </is>
       </c>
       <c r="C20" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/03-Test_File_Extensions_Handling_for_Sensitive_Information", "Test File Extensions Handling for Sensitive Information")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/03-Test_File_Extensions_Handling_for_Sensitive_Information", "Probar Manejo de Extensiones de Archivo para Información Sensible")</f>
         <v/>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>- Brute force sensitive file extensions that might contain raw data such as scripts, credentials, etc.
-- Validate that no system framework bypasses exist for the rules that have been set</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
@@ -1882,7 +1878,7 @@
       </c>
       <c r="F20" s="18" t="n"/>
     </row>
-    <row r="21" ht="33" customHeight="1" s="82">
+    <row r="21" ht="49.5" customHeight="1" s="82">
       <c r="A21" s="19" t="n"/>
       <c r="B21" s="34" t="inlineStr">
         <is>
@@ -1890,12 +1886,12 @@
         </is>
       </c>
       <c r="C21" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/04-Review_Old_Backup_and_Unreferenced_Files_for_Sensitive_Information", "Review Old Backup and Unreferenced Files for Sensitive Information")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/04-Review_Old_Backup_and_Unreferenced_Files_for_Sensitive_Information", "Revisar Archivos Antiguos de Respaldo y No Referenciados para Información Sensible")</f>
         <v/>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>- Find and analyse unreferenced files that might contain sensitive information.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
@@ -1913,12 +1909,12 @@
         </is>
       </c>
       <c r="C22" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/05-Enumerate_Infrastructure_and_Application_Admin_Interfaces", "Enumerate Infrastructure and Application Admin Interfaces")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/05-Enumerate_Infrastructure_and_Application_Admin_Interfaces", "Enumerar Interfaces de Administración de Infraestructura y Aplicación")</f>
         <v/>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>- Identify hidden administrator interfaces and functionality.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E22" s="18" t="inlineStr">
@@ -1928,7 +1924,7 @@
       </c>
       <c r="F22" s="18" t="n"/>
     </row>
-    <row r="23" ht="49.5" customHeight="1" s="82">
+    <row r="23" ht="16.5" customHeight="1" s="82">
       <c r="A23" s="19" t="n"/>
       <c r="B23" s="34" t="inlineStr">
         <is>
@@ -1936,14 +1932,12 @@
         </is>
       </c>
       <c r="C23" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/06-Test_HTTP_Methods", "Test HTTP Methods")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/06-Test_HTTP_Methods", "Probar Métodos HTTP")</f>
         <v/>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>- Enumerate supported HTTP methods.
-- Test for access control bypass.
-- Test HTTP method overriding techniques.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
@@ -1961,12 +1955,12 @@
         </is>
       </c>
       <c r="C24" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/07-Test_HTTP_Strict_Transport_Security", "Test HTTP Strict Transport Security")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/07-Test_HTTP_Strict_Transport_Security", "Prueba de HTTP Strict Transport Security")</f>
         <v/>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>- Review the HSTS header and its validity.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
@@ -1984,7 +1978,7 @@
         </is>
       </c>
       <c r="C25" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/08-Test_RIA_Cross_Domain_Policy", "Test RIA Cross Domain Policy")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/08-Test_RIA_Cross_Domain_Policy", "Probar Política de Dominio Cruzado RIA")</f>
         <v/>
       </c>
       <c r="D25" s="16" t="inlineStr">
@@ -2007,12 +2001,12 @@
         </is>
       </c>
       <c r="C26" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/09-Test_File_Permission", "Test File Permission")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/09-Test_File_Permission", "Probar Permisos de Archivo")</f>
         <v/>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>- Review and identify any rogue file permissions.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
@@ -2100,12 +2094,12 @@
         </is>
       </c>
       <c r="C30" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/13-Test_for_Path_Confusion", "Test Path Confusion")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/13-Test_for_Path_Confusion", "Probar Path Confusion")</f>
         <v/>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>- Make sure application paths are configured correctly.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
@@ -2176,7 +2170,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="66" customHeight="1" s="82">
+    <row r="34" ht="16.5" customHeight="1" s="82">
       <c r="A34" s="19" t="n"/>
       <c r="B34" s="34" t="inlineStr">
         <is>
@@ -2184,14 +2178,12 @@
         </is>
       </c>
       <c r="C34" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/01-Test_Role_Definitions", "Test Role Definitions")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/01-Test_Role_Definitions", "Prueba de Definiciones de Roles")</f>
         <v/>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>- Identify and document roles used by the application.
-- Attempt to switch, change, or access another role.
-- Review the granularity of the roles and the needs behind the permissions given.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
@@ -2201,7 +2193,7 @@
       </c>
       <c r="F34" s="18" t="n"/>
     </row>
-    <row r="35" ht="49.5" customHeight="1" s="82">
+    <row r="35" ht="16.5" customHeight="1" s="82">
       <c r="A35" s="19" t="n"/>
       <c r="B35" s="34" t="inlineStr">
         <is>
@@ -2209,13 +2201,12 @@
         </is>
       </c>
       <c r="C35" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/02-Test_User_Registration_Process", "Test User Registration Process")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/02-Test_User_Registration_Process", "Probar Proceso de Registro de Usuario")</f>
         <v/>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>- Verify that the identity requirements for user registration are aligned with business and security requirements.
-- Validate the registration process.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr">
@@ -2225,7 +2216,7 @@
       </c>
       <c r="F35" s="18" t="n"/>
     </row>
-    <row r="36" ht="33" customHeight="1" s="82">
+    <row r="36" ht="16.5" customHeight="1" s="82">
       <c r="A36" s="19" t="n"/>
       <c r="B36" s="34" t="inlineStr">
         <is>
@@ -2233,12 +2224,12 @@
         </is>
       </c>
       <c r="C36" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/03-Test_Account_Provisioning_Process", "Test Account Provisioning Process")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/03-Test_Account_Provisioning_Process", "Probar Proceso de Provisioning de Cuenta")</f>
         <v/>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>- Verify which accounts may provision other accounts and of what type.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E36" s="18" t="inlineStr">
@@ -2272,7 +2263,7 @@
       </c>
       <c r="F37" s="18" t="n"/>
     </row>
-    <row r="38" ht="66" customHeight="1" s="82">
+    <row r="38" ht="33" customHeight="1" s="82">
       <c r="A38" s="19" t="n"/>
       <c r="B38" s="34" t="inlineStr">
         <is>
@@ -2280,13 +2271,12 @@
         </is>
       </c>
       <c r="C38" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/05-Testing_for_Weak_or_Unenforced_Username_Policy", "Testing for Weak or Unenforced Username Policy")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/05-Testing_for_Weak_or_Unenforced_Username_Policy", "Pruebas de Política de Nombre de Usuario Débil o No Impuesta")</f>
         <v/>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>- Determine whether a consistent account name structure renders the application vulnerable to account enumeration.
-- Determine whether the application's error messages permit account enumeration.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E38" s="18" t="inlineStr">
@@ -2340,7 +2330,7 @@
         </is>
       </c>
       <c r="C41" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/01-Testing_for_Credentials_Transported_over_an_Encrypted_Channel", "Testing for Credentials Transported over an Encrypted Channel")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/01-Testing_for_Credentials_Transported_over_an_Encrypted_Channel", "Prueba de credenciales transportadas a través de un canal encriptado")</f>
         <v/>
       </c>
       <c r="D41" s="16" t="inlineStr">
@@ -2355,7 +2345,7 @@
       </c>
       <c r="F41" s="18" t="n"/>
     </row>
-    <row r="42" ht="66" customHeight="1" s="82">
+    <row r="42" ht="16.5" customHeight="1" s="82">
       <c r="A42" s="19" t="n"/>
       <c r="B42" s="34" t="inlineStr">
         <is>
@@ -2363,13 +2353,12 @@
         </is>
       </c>
       <c r="C42" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/02-Testing_for_Default_Credentials", "Testing for Default Credentials")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/02-Testing_for_Default_Credentials", "Pruebas de credenciales predeterminadas")</f>
         <v/>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>- Determine whether the application has any user accounts with default passwords.
-- Review whether new user accounts are created with weak or predictable passwords.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E42" s="18" t="inlineStr">
@@ -2379,7 +2368,7 @@
       </c>
       <c r="F42" s="18" t="n"/>
     </row>
-    <row r="43" ht="66" customHeight="1" s="82">
+    <row r="43" ht="16.5" customHeight="1" s="82">
       <c r="A43" s="19" t="n"/>
       <c r="B43" s="34" t="inlineStr">
         <is>
@@ -2387,13 +2376,12 @@
         </is>
       </c>
       <c r="C43" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/03-Testing_for_Weak_Lock_Out_Mechanism", "Testing for Weak Lock Out Mechanism")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/03-Testing_for_Weak_Lock_Out_Mechanism", "Prueba de Mecanismos de Bloqueo Débiles")</f>
         <v/>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>- Evaluate the account lockout mechanism's ability to mitigate brute force password guessing.
-- Evaluate the unlock mechanism's resistance to unauthorized account unlocking.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr">
@@ -2411,12 +2399,12 @@
         </is>
       </c>
       <c r="C44" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/04-Testing_for_Bypassing_Authentication_Schema", "Testing for Bypassing Authentication Schema")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/04-Testing_for_Bypassing_Authentication_Schema", "Pruebas de omisión del esquema de autenticación")</f>
         <v/>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>- Ensure that authentication is applied across all services that require it.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
@@ -2434,12 +2422,12 @@
         </is>
       </c>
       <c r="C45" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/05-Testing_for_Vulnerable_Remember_Password", "Testing for Vulnerable Remember Password")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/05-Testing_for_Vulnerable_Remember_Password", "Pruebas de contraseñas recordadas vulnerables")</f>
         <v/>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>- Validate that the generated session is managed securely and do not put the user's credentials in danger.</t>
+          <t>- Validar que la sesión generada se gestione de manera segura y no ponga en peligro las credenciales del usuario.</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
@@ -2457,13 +2445,13 @@
         </is>
       </c>
       <c r="C46" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/06-Testing_for_Browser_Cache_Weaknesses", "Testing for Browser Cache Weaknesses")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/06-Testing_for_Browser_Cache_Weaknesses", "Pruebas de debilidades en la caché del navegador")</f>
         <v/>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>- Review if the application stores sensitive information on the client-side.
-- Review if access can occur without authorization.</t>
+          <t>- Revisar si la aplicación almacena información sensible en el lado del cliente.
+- Revisar si se puede acceder sin autorización.</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
@@ -2473,7 +2461,7 @@
       </c>
       <c r="F46" s="18" t="n"/>
     </row>
-    <row r="47" ht="66" customHeight="1" s="82">
+    <row r="47" ht="33" customHeight="1" s="82">
       <c r="A47" s="19" t="n"/>
       <c r="B47" s="34" t="inlineStr">
         <is>
@@ -2481,12 +2469,12 @@
         </is>
       </c>
       <c r="C47" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/07-Testing_for_Weak_Authentication_Methods", "Testing for Weak Authentication Methods")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/07-Testing_for_Weak_Authentication_Methods", "Pruebas de métodos de autenticación débiles")</f>
         <v/>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>- Determine the resistance of the application against brute force password guessing using available password dictionaries by evaluating the length, complexity, reuse, and aging requirements of passwords.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr">
@@ -2496,7 +2484,7 @@
       </c>
       <c r="F47" s="18" t="n"/>
     </row>
-    <row r="48" ht="49.5" customHeight="1" s="82">
+    <row r="48" ht="33" customHeight="1" s="82">
       <c r="A48" s="19" t="n"/>
       <c r="B48" s="34" t="inlineStr">
         <is>
@@ -2504,13 +2492,12 @@
         </is>
       </c>
       <c r="C48" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/08-Testing_for_Weak_Security_Question_Answer", "Testing for Weak Security Question Answer")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/08-Testing_for_Weak_Security_Question_Answer", "Pruebas de preguntas de seguridad débiles")</f>
         <v/>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>- Determine the complexity and how straight-forward the questions are.
-- Assess possible user answers and brute force capabilities.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E48" s="18" t="inlineStr">
@@ -2528,12 +2515,12 @@
         </is>
       </c>
       <c r="C49" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/09-Testing_for_Weak_Password_Change_or_Reset_Functionalities", "Testing for Weak Password Change or Reset Functionalities")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/09-Testing_for_Weak_Password_Change_or_Reset_Functionalities", "Pruebas de Funcionalidades Débiles de Cambio o Restablecimiento de Contraseña")</f>
         <v/>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>- Determine whether the password change and reset functionality allows accounts to be compromised.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr">
@@ -2543,7 +2530,7 @@
       </c>
       <c r="F49" s="18" t="n"/>
     </row>
-    <row r="50" ht="49.5" customHeight="1" s="82">
+    <row r="50" ht="33" customHeight="1" s="82">
       <c r="A50" s="19" t="n"/>
       <c r="B50" s="34" t="inlineStr">
         <is>
@@ -2551,13 +2538,12 @@
         </is>
       </c>
       <c r="C50" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/10-Testing_for_Weaker_Authentication_in_Alternative_Channel", "Testing for Weaker Authentication in Alternative Channel")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/10-Testing_for_Weaker_Authentication_in_Alternative_Channel", "Pruebas de autenticación más débil en canales alternativos")</f>
         <v/>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>- Identify alternative authentication channels.
-- Assess the security measures used and if any bypasses exists on the alternative channels.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E50" s="18" t="inlineStr">
@@ -2567,7 +2553,7 @@
       </c>
       <c r="F50" s="18" t="n"/>
     </row>
-    <row r="51" ht="66" customHeight="1" s="82">
+    <row r="51" ht="33" customHeight="1" s="82">
       <c r="A51" s="19" t="n"/>
       <c r="B51" s="34" t="inlineStr">
         <is>
@@ -2575,14 +2561,12 @@
         </is>
       </c>
       <c r="C51" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/11-Testing_Multi-Factor_Authentication", "Testing Multi-Factor Authentication (MFA)")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/04-Authentication_Testing/11-Testing_Multi-Factor_Authentication", "Pruebas de Autenticación Multifactor (MFA)")</f>
         <v/>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>- Identify the type of MFA used by the application.
-- Determine whether the MFA implementation is robust and secure.
-- Attempt to bypass the MFA.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr">
@@ -2628,7 +2612,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="49.5" customHeight="1" s="82">
+    <row r="54" ht="33" customHeight="1" s="82">
       <c r="A54" s="19" t="n"/>
       <c r="B54" s="34" t="inlineStr">
         <is>
@@ -2636,13 +2620,12 @@
         </is>
       </c>
       <c r="C54" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/01-Testing_Directory_Traversal_File_Include", "Testing Directory Traversal File Include")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/01-Testing_Directory_Traversal_File_Include", "Pruebas de Traversal de Directorio e Inclusión de Archivos")</f>
         <v/>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>- Identify injection points that pertain to path traversal.
-- Assess bypassing techniques and identify the extent of path traversal.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E54" s="18" t="inlineStr">
@@ -2660,12 +2643,12 @@
         </is>
       </c>
       <c r="C55" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/02-Testing_for_Bypassing_Authorization_Schema", "Testing for Bypassing Authorization Schema")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/02-Testing_for_Bypassing_Authorization_Schema", "Pruebas de omisión del esquema de autorización")</f>
         <v/>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>- Assess if unauthenticated, horizontal, or vertical access is possible.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr">
@@ -2675,7 +2658,7 @@
       </c>
       <c r="F55" s="18" t="n"/>
     </row>
-    <row r="56" ht="49.5" customHeight="1" s="82">
+    <row r="56" ht="16.5" customHeight="1" s="82">
       <c r="A56" s="19" t="n"/>
       <c r="B56" s="34" t="inlineStr">
         <is>
@@ -2683,13 +2666,12 @@
         </is>
       </c>
       <c r="C56" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/03-Testing_for_Privilege_Escalation", "Testing for Privilege Escalation")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/03-Testing_for_Privilege_Escalation", "Pruebas de Escalada de Privilegios")</f>
         <v/>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>- Identify injection points related to privilege manipulation.
-- Fuzz or otherwise attempt to bypass security measures.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E56" s="18" t="inlineStr">
@@ -2699,7 +2681,7 @@
       </c>
       <c r="F56" s="18" t="n"/>
     </row>
-    <row r="57" ht="49.5" customHeight="1" s="82">
+    <row r="57" ht="66" customHeight="1" s="82">
       <c r="A57" s="19" t="n"/>
       <c r="B57" s="34" t="inlineStr">
         <is>
@@ -2707,13 +2689,13 @@
         </is>
       </c>
       <c r="C57" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/04-Testing_for_Insecure_Direct_Object_References", "Testing for Insecure Direct Object References")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/04-Testing_for_Insecure_Direct_Object_References", "Pruebas de referencias directas a objetos inseguras")</f>
         <v/>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>- Identify points where object references may occur.
-- Assess the access control measures and if they're vulnerable to IDOR.</t>
+          <t>- Identificar puntos donde pueden ocurrir referencias a objetos.
+- Evaluar las medidas de control de acceso y si son vulnerables a IDOR.</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr">
@@ -2782,7 +2764,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="99" customHeight="1" s="82">
+    <row r="61" ht="33" customHeight="1" s="82">
       <c r="A61" s="19" t="n"/>
       <c r="B61" s="34" t="inlineStr">
         <is>
@@ -2790,14 +2772,12 @@
         </is>
       </c>
       <c r="C61" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/01-Testing_for_Session_Management_Schema", "Testing for Session Management Schema")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/01-Testing_for_Session_Management_Schema", "Pruebas del Esquema de Gestión de Sesiones")</f>
         <v/>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>- Gather session tokens, for the same user and for different users where possible.
-- Analyze and ensure that enough randomness exists to stop session forging attacks.
-- Modify cookies that are not signed and contain information that can be manipulated.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr">
@@ -2807,7 +2787,7 @@
       </c>
       <c r="F61" s="18" t="n"/>
     </row>
-    <row r="62" ht="33" customHeight="1" s="82">
+    <row r="62" ht="16.5" customHeight="1" s="82">
       <c r="A62" s="19" t="n"/>
       <c r="B62" s="34" t="inlineStr">
         <is>
@@ -2815,12 +2795,12 @@
         </is>
       </c>
       <c r="C62" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/02-Testing_for_Cookies_Attributes", "Testing for Cookies Attributes")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/02-Testing_for_Cookies_Attributes", "Pruebas de atributos de cookies")</f>
         <v/>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>- Ensure that the proper security configuration is set for cookies.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E62" s="18" t="inlineStr">
@@ -2830,7 +2810,7 @@
       </c>
       <c r="F62" s="18" t="n"/>
     </row>
-    <row r="63" ht="33" customHeight="1" s="82">
+    <row r="63" ht="16.5" customHeight="1" s="82">
       <c r="A63" s="19" t="n"/>
       <c r="B63" s="34" t="inlineStr">
         <is>
@@ -2838,13 +2818,12 @@
         </is>
       </c>
       <c r="C63" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/03-Testing_for_Session_Fixation", "Testing for Session Fixation")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/03-Testing_for_Session_Fixation", "Prueba de fijación de sesión")</f>
         <v/>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>- Analyze the authentication mechanism and its flow.
-- Force cookies and assess the impact.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr">
@@ -2854,7 +2833,7 @@
       </c>
       <c r="F63" s="18" t="n"/>
     </row>
-    <row r="64" ht="49.5" customHeight="1" s="82">
+    <row r="64" ht="16.5" customHeight="1" s="82">
       <c r="A64" s="19" t="n"/>
       <c r="B64" s="34" t="inlineStr">
         <is>
@@ -2862,14 +2841,12 @@
         </is>
       </c>
       <c r="C64" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/04-Testing_for_Exposed_Session_Variables", "Testing for Exposed Session Variables")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/04-Testing_for_Exposed_Session_Variables", "Pruebas de Variables de Sesión Expuestas")</f>
         <v/>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>- Ensure that proper encryption is implemented.
-- Review the caching configuration.
-- Assess the channel and methods' security.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E64" s="18" t="inlineStr">
@@ -2887,12 +2864,12 @@
         </is>
       </c>
       <c r="C65" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/05-Testing_for_Cross_Site_Request_Forgery", "Testing for Cross Site Request Forgery")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/05-Testing_for_Cross_Site_Request_Forgery", "Prueba de Falsificación de Solicitud entre Sitios")</f>
         <v/>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>- Determine whether it is possible to initiate requests on a user's behalf that are not initiated by the user.</t>
+          <t>- Determinar si es posible iniciar solicitudes en nombre de un usuario que no son iniciadas por el usuario.</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr">
@@ -2902,7 +2879,7 @@
       </c>
       <c r="F65" s="18" t="n"/>
     </row>
-    <row r="66" ht="49.5" customHeight="1" s="82">
+    <row r="66" ht="33" customHeight="1" s="82">
       <c r="A66" s="19" t="n"/>
       <c r="B66" s="34" t="inlineStr">
         <is>
@@ -2910,13 +2887,12 @@
         </is>
       </c>
       <c r="C66" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/06-Testing_for_Logout_Functionality", "Testing for Logout Functionality")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/06-Testing_for_Logout_Functionality", "Pruebas de funcionalidad de cierre de sesión")</f>
         <v/>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>- Assess the logout UI.
-- Analyze the session timeout and if the session is properly killed after logout.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E66" s="18" t="inlineStr">
@@ -2934,12 +2910,12 @@
         </is>
       </c>
       <c r="C67" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/07-Testing_Session_Timeout", "Testing Session Timeout")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/07-Testing_Session_Timeout", "Prueba de tiempo de espera de sesión")</f>
         <v/>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>- Validate that a hard session timeout exists.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr">
@@ -2949,7 +2925,7 @@
       </c>
       <c r="F67" s="18" t="n"/>
     </row>
-    <row r="68" ht="33" customHeight="1" s="82">
+    <row r="68" ht="16.5" customHeight="1" s="82">
       <c r="A68" s="19" t="n"/>
       <c r="B68" s="34" t="inlineStr">
         <is>
@@ -2957,13 +2933,12 @@
         </is>
       </c>
       <c r="C68" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/08-Testing_for_Session_Puzzling", "Testing for Session Puzzling")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/08-Testing_for_Session_Puzzling", "Pruebas de Confusión de Sesión")</f>
         <v/>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>- Identify all session variables.
-- Break the logical flow of session generation.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E68" s="18" t="inlineStr">
@@ -2973,7 +2948,7 @@
       </c>
       <c r="F68" s="18" t="n"/>
     </row>
-    <row r="69" ht="33" customHeight="1" s="82">
+    <row r="69" ht="16.5" customHeight="1" s="82">
       <c r="A69" s="19" t="n"/>
       <c r="B69" s="34" t="inlineStr">
         <is>
@@ -2981,13 +2956,12 @@
         </is>
       </c>
       <c r="C69" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/09-Testing_for_Session_Hijacking", "Testing for Session Hijacking")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/09-Testing_for_Session_Hijacking", "Pruebas de Secuestro de Sesión")</f>
         <v/>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>- Identify vulnerable session cookies.
-- Hijack vulnerable cookies and assess the risk level.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr">
@@ -2997,7 +2971,7 @@
       </c>
       <c r="F69" s="18" t="n"/>
     </row>
-    <row r="70" ht="49.5" customHeight="1" s="82">
+    <row r="70" ht="16.5" customHeight="1" s="82">
       <c r="A70" s="19" t="n"/>
       <c r="B70" s="34" t="inlineStr">
         <is>
@@ -3005,13 +2979,12 @@
         </is>
       </c>
       <c r="C70" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/10-Testing_JSON_Web_Tokens", "Testing JSON Web Tokens")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/10-Testing_JSON_Web_Tokens", "Pruebas de JSON Web Tokens")</f>
         <v/>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>- Determine whether the JWTs expose sensitive information.
-- Determine whether the JWTs can be tampered with or modified.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E70" s="18" t="inlineStr">
@@ -3021,7 +2994,7 @@
       </c>
       <c r="F70" s="18" t="n"/>
     </row>
-    <row r="71" ht="49.5" customHeight="1" s="82">
+    <row r="71" ht="16.5" customHeight="1" s="82">
       <c r="A71" s="19" t="n"/>
       <c r="B71" s="34" t="inlineStr">
         <is>
@@ -3029,12 +3002,12 @@
         </is>
       </c>
       <c r="C71" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/11-Testing_for_Concurrent_Sessions", "Testing for Concurrent Sessions")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/06-Session_Management_Testing/11-Testing_for_Concurrent_Sessions", "Pruebas de Sesiones Concurrentes")</f>
         <v/>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>- Evaluate the application's session management by assessing the handling of multiple active sessions for a single user account.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr">
@@ -3080,7 +3053,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="49.5" customHeight="1" s="82">
+    <row r="74" ht="33" customHeight="1" s="82">
       <c r="A74" s="19" t="n"/>
       <c r="B74" s="34" t="inlineStr">
         <is>
@@ -3088,13 +3061,12 @@
         </is>
       </c>
       <c r="C74" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/01-Testing_for_Reflected_Cross_Site_Scripting", "Testing for Reflected Cross Site Scripting")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/01-Testing_for_Reflected_Cross_Site_Scripting", "Pruebas de scripting entre sitios reflejado")</f>
         <v/>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>- Identify variables that are reflected in responses.
-- Assess the input they accept and the encoding that gets applied on return (if any).</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E74" s="18" t="inlineStr">
@@ -3104,7 +3076,7 @@
       </c>
       <c r="F74" s="18" t="n"/>
     </row>
-    <row r="75" ht="66" customHeight="1" s="82">
+    <row r="75" ht="33" customHeight="1" s="82">
       <c r="A75" s="19" t="n"/>
       <c r="B75" s="34" t="inlineStr">
         <is>
@@ -3112,13 +3084,12 @@
         </is>
       </c>
       <c r="C75" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/02-Testing_for_Stored_Cross_Site_Scripting", "Testing for Stored Cross Site Scripting")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/02-Testing_for_Stored_Cross_Site_Scripting", "Pruebas de Scripting entre Sitios Almacenado")</f>
         <v/>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>- Identify stored input that is reflected on the client-side.
-- Assess the input they accept and the encoding that gets applied on return (if any).</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr">
@@ -3136,7 +3107,7 @@
         </is>
       </c>
       <c r="C76" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/03-Testing_for_HTTP_Verb_Tampering", "Testing for HTTP Verb Tampering")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/03-Testing_for_HTTP_Verb_Tampering", "Pruebas de manipulación de verbos HTTP")</f>
         <v/>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -3151,7 +3122,7 @@
       </c>
       <c r="F76" s="18" t="n"/>
     </row>
-    <row r="77" ht="49.5" customHeight="1" s="82">
+    <row r="77" ht="33" customHeight="1" s="82">
       <c r="A77" s="19" t="n"/>
       <c r="B77" s="34" t="inlineStr">
         <is>
@@ -3159,13 +3130,12 @@
         </is>
       </c>
       <c r="C77" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/04-Testing_for_HTTP_Parameter_Pollution", "Testing for HTTP Parameter Pollution")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/04-Testing_for_HTTP_Parameter_Pollution", "Pruebas de Contaminación de Parámetros HTTP")</f>
         <v/>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>- Identify the backend and the parsing method used.
-- Assess injection points and try bypassing input filters using HPP.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr">
@@ -3188,8 +3158,8 @@
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>- Identify SQL injection points.
-- Assess the severity of the injection and the level of access that can be achieved through it.</t>
+          <t>- Identificar puntos de inyección SQL.
+- Evaluar la gravedad de la inyección y el nivel de acceso que se puede lograr a través de ella.</t>
         </is>
       </c>
       <c r="E78" s="18" t="inlineStr">
@@ -3199,7 +3169,7 @@
       </c>
       <c r="F78" s="18" t="n"/>
     </row>
-    <row r="79" ht="33" customHeight="1" s="82">
+    <row r="79" ht="16.5" customHeight="1" s="82">
       <c r="A79" s="19" t="n"/>
       <c r="B79" s="34" t="inlineStr">
         <is>
@@ -3207,13 +3177,12 @@
         </is>
       </c>
       <c r="C79" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/06-Testing_for_LDAP_Injection", "Testing for LDAP Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/06-Testing_for_LDAP_Injection", "Pruebas de Inyección LDAP")</f>
         <v/>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>- Identify LDAP injection points.
-- Assess the severity of the injection.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr">
@@ -3223,7 +3192,7 @@
       </c>
       <c r="F79" s="18" t="n"/>
     </row>
-    <row r="80" ht="49.5" customHeight="1" s="82">
+    <row r="80" ht="16.5" customHeight="1" s="82">
       <c r="A80" s="19" t="n"/>
       <c r="B80" s="34" t="inlineStr">
         <is>
@@ -3231,13 +3200,12 @@
         </is>
       </c>
       <c r="C80" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/07-Testing_for_XML_Injection", "Testing for XML Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/07-Testing_for_XML_Injection", "Pruebas de Inyección XML")</f>
         <v/>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>- Identify XML injection points.
-- Assess the types of exploits that can be attained and their severities.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E80" s="18" t="inlineStr">
@@ -3247,7 +3215,7 @@
       </c>
       <c r="F80" s="18" t="n"/>
     </row>
-    <row r="81" ht="33" customHeight="1" s="82">
+    <row r="81" ht="16.5" customHeight="1" s="82">
       <c r="A81" s="19" t="n"/>
       <c r="B81" s="34" t="inlineStr">
         <is>
@@ -3255,13 +3223,12 @@
         </is>
       </c>
       <c r="C81" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/08-Testing_for_SSI_Injection", "Testing for SSI Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/08-Testing_for_SSI_Injection", "Prueba de inyección SSI")</f>
         <v/>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>- Identify SSI injection points.
-- Assess the severity of the injection.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr">
@@ -3279,12 +3246,12 @@
         </is>
       </c>
       <c r="C82" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/09-Testing_for_XPath_Injection", "Testing for XPath Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/09-Testing_for_XPath_Injection", "Pruebas de inyección XPath")</f>
         <v/>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>- Identify XPATH injection points.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E82" s="18" t="inlineStr">
@@ -3294,7 +3261,7 @@
       </c>
       <c r="F82" s="18" t="n"/>
     </row>
-    <row r="83" ht="66" customHeight="1" s="82">
+    <row r="83" ht="16.5" customHeight="1" s="82">
       <c r="A83" s="19" t="n"/>
       <c r="B83" s="34" t="inlineStr">
         <is>
@@ -3302,14 +3269,12 @@
         </is>
       </c>
       <c r="C83" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/10-Testing_for_IMAP_SMTP_Injection", "Testing for IMAP SMTP Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/10-Testing_for_IMAP_SMTP_Injection", "Prueba de inyección IMAP SMTP")</f>
         <v/>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>- Identify IMAP/SMTP injection points.
-- Understand the data flow and deployment structure of the system.
-- Assess the injection impacts.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr">
@@ -3319,7 +3284,7 @@
       </c>
       <c r="F83" s="18" t="n"/>
     </row>
-    <row r="84" ht="49.5" customHeight="1" s="82">
+    <row r="84" ht="16.5" customHeight="1" s="82">
       <c r="A84" s="19" t="n"/>
       <c r="B84" s="34" t="inlineStr">
         <is>
@@ -3327,13 +3292,12 @@
         </is>
       </c>
       <c r="C84" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/11-Testing_for_Code_Injection", "Testing for Code Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/11-Testing_for_Code_Injection", "Pruebas de inyección de código")</f>
         <v/>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>- Identify injection points where you can inject code into the application.
-- Assess the injection severity.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E84" s="18" t="inlineStr">
@@ -3351,12 +3315,12 @@
         </is>
       </c>
       <c r="C85" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/12-Testing_for_Command_Injection", "Testing for Command Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/12-Testing_for_Command_Injection", "Prueba de inyección de comandos")</f>
         <v/>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>- Identify and assess the command injection points.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr">
@@ -3374,7 +3338,7 @@
         </is>
       </c>
       <c r="C86" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/13-Testing_for_Buffer_Overflow", "Testing for Buffer Overflow")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/13-Testing_for_Buffer_Overflow", "Pruebas de Desbordamiento de Búfer")</f>
         <v/>
       </c>
       <c r="D86" s="16" t="inlineStr">
@@ -3389,7 +3353,7 @@
       </c>
       <c r="F86" s="18" t="n"/>
     </row>
-    <row r="87" ht="49.5" customHeight="1" s="82">
+    <row r="87" ht="33" customHeight="1" s="82">
       <c r="A87" s="19" t="n"/>
       <c r="B87" s="34" t="inlineStr">
         <is>
@@ -3397,12 +3361,12 @@
         </is>
       </c>
       <c r="C87" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/13-Testing_for_Format_String_Injection", "Testing for Format String Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/13-Testing_for_Format_String_Injection", "Pruebas de inyección de cadena de formato")</f>
         <v/>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>- Assess whether injecting format string conversion specifiers into user-controlled fields causes undesired behavior from the application.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr">
@@ -3412,7 +3376,7 @@
       </c>
       <c r="F87" s="18" t="n"/>
     </row>
-    <row r="88" ht="66" customHeight="1" s="82">
+    <row r="88" ht="16.5" customHeight="1" s="82">
       <c r="A88" s="19" t="n"/>
       <c r="B88" s="34" t="inlineStr">
         <is>
@@ -3420,14 +3384,12 @@
         </is>
       </c>
       <c r="C88" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/14-Testing_for_Incubated_Vulnerability", "Testing for Incubated Vulnerability")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/14-Testing_for_Incubated_Vulnerability", "Prueba de vulnerabilidades incubadas")</f>
         <v/>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>- Identify injections that are stored and require a recall step to the stored injection.
-- Understand how a recall step could occur.
-- Set listeners or activate the recall step if possible.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E88" s="18" t="inlineStr">
@@ -3437,7 +3399,7 @@
       </c>
       <c r="F88" s="18" t="n"/>
     </row>
-    <row r="89" ht="66" customHeight="1" s="82">
+    <row r="89" ht="115.5" customHeight="1" s="82">
       <c r="A89" s="19" t="n"/>
       <c r="B89" s="34" t="inlineStr">
         <is>
@@ -3445,13 +3407,14 @@
         </is>
       </c>
       <c r="C89" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/15-Testing_for_HTTP_Splitting_Smuggling", "Testing for HTTP Splitting Smuggling")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/15-Testing_for_HTTP_Response_Splitting", "Testing for HTTP Response Splitting")</f>
         <v/>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>- Assess if the application is vulnerable to splitting, identifying what possible attacks are achievable.
-- Assess if the chain of communication is vulnerable to smuggling, identifying what possible attacks are achievable.</t>
+          <t>- Identify user-controlled input that is reflected into HTTP response headers.
+- Assess whether CR (`\r`) and LF (`\n`) characters can be injected into response headers.
+- Determine the potential impact of successful HTTP Response Splitting attacks, such as cache poisoning or client-side exploitation.</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr">
@@ -3461,7 +3424,7 @@
       </c>
       <c r="F89" s="18" t="n"/>
     </row>
-    <row r="90" ht="66" customHeight="1" s="82">
+    <row r="90" ht="99" customHeight="1" s="82">
       <c r="A90" s="19" t="n"/>
       <c r="B90" s="34" t="inlineStr">
         <is>
@@ -3469,13 +3432,16 @@
         </is>
       </c>
       <c r="C90" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/16-Testing_for_HTTP_Incoming_Requests", "Testing for HTTP Incoming Requests")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/16-Testing_for_HTTP_Request_Smuggling", "Testing for HTTP Request Smuggling")</f>
         <v/>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>- Monitor all incoming and outgoing HTTP requests to the Web Server to inspect any suspicious requests.
-- Monitor HTTP traffic without changes of end user Browser proxy or client-side application.</t>
+          <t>- Identify request boundary inconsistencies between frontend and backend components
+- Detect classic CL/TE desynchronization vulnerabilities
+- Evaluate protocol translation logic (HTTP/2 → HTTP/1.1)
+- Assess H2C upgrade handling and downgrade safety
+- Confirm backend request queue poisoning</t>
         </is>
       </c>
       <c r="E90" s="18" t="inlineStr">
@@ -3485,7 +3451,7 @@
       </c>
       <c r="F90" s="18" t="n"/>
     </row>
-    <row r="91" ht="49.5" customHeight="1" s="82">
+    <row r="91" ht="16.5" customHeight="1" s="82">
       <c r="A91" s="19" t="n"/>
       <c r="B91" s="34" t="inlineStr">
         <is>
@@ -3493,13 +3459,12 @@
         </is>
       </c>
       <c r="C91" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/17-Testing_for_Host_Header_Injection", "Testing for Host Header Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/17-Testing_for_Host_Header_Injection", "Pruebas de inyección de cabecera Host")</f>
         <v/>
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>- Assess if the Host header is being parsed dynamically in the application.
-- Bypass security controls that rely on the header.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr">
@@ -3509,7 +3474,7 @@
       </c>
       <c r="F91" s="18" t="n"/>
     </row>
-    <row r="92" ht="49.5" customHeight="1" s="82">
+    <row r="92" ht="33" customHeight="1" s="82">
       <c r="A92" s="19" t="n"/>
       <c r="B92" s="34" t="inlineStr">
         <is>
@@ -3517,14 +3482,12 @@
         </is>
       </c>
       <c r="C92" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/18-Testing_for_Server-side_Template_Injection", "Testing for Server-side Template Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/18-Testing_for_Server-side_Template_Injection", "Pruebas de inyección de plantillas del lado del servidor")</f>
         <v/>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>- Detect template injection vulnerability points.
-- Identify the templating engine.
-- Build the exploit.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E92" s="18" t="inlineStr">
@@ -3534,7 +3497,7 @@
       </c>
       <c r="F92" s="18" t="n"/>
     </row>
-    <row r="93" ht="49.5" customHeight="1" s="82">
+    <row r="93" ht="33" customHeight="1" s="82">
       <c r="A93" s="19" t="n"/>
       <c r="B93" s="34" t="inlineStr">
         <is>
@@ -3542,14 +3505,12 @@
         </is>
       </c>
       <c r="C93" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/19-Testing_for_Server-Side_Request_Forgery", "Testing for Server-Side Request Forgery")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/19-Testing_for_Server-Side_Request_Forgery", "Pruebas para falsificación de solicitudes del lado del servidor")</f>
         <v/>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>- Identify SSRF injection points.
-- Test if the injection points are exploitable.
-- Asses the severity of the vulnerability.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr">
@@ -3559,7 +3520,7 @@
       </c>
       <c r="F93" s="18" t="n"/>
     </row>
-    <row r="94" ht="49.5" customHeight="1" s="82">
+    <row r="94" ht="16.5" customHeight="1" s="82">
       <c r="A94" s="19" t="n"/>
       <c r="B94" s="34" t="inlineStr">
         <is>
@@ -3567,13 +3528,12 @@
         </is>
       </c>
       <c r="C94" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/20-Testing_for_Mass_Assignment", "Testing for Mass Assignment")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/20-Testing_for_Mass_Assignment", "Pruebas de asignación masiva")</f>
         <v/>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>- Identify requests that modify objects
-- Assess if it is possible to modify fields never intended to be modified from outside</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E94" s="18" t="inlineStr">
@@ -3583,189 +3543,184 @@
       </c>
       <c r="F94" s="18" t="n"/>
     </row>
-    <row r="95" ht="15" customHeight="1" s="82">
-      <c r="A95" s="97" t="n"/>
-      <c r="B95" s="98" t="n"/>
-      <c r="C95" s="99" t="n"/>
-      <c r="D95" s="99" t="n"/>
-      <c r="E95" s="99" t="n"/>
-      <c r="F95" s="99" t="n"/>
-    </row>
-    <row r="96" ht="47.25" customHeight="1" s="82">
-      <c r="A96" s="9" t="n"/>
-      <c r="B96" s="100" t="inlineStr">
+    <row r="95" ht="16.5" customHeight="1" s="82">
+      <c r="A95" s="19" t="n"/>
+      <c r="B95" s="34" t="inlineStr">
+        <is>
+          <t>WSTG-INPV-21</t>
+        </is>
+      </c>
+      <c r="C95" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/21-Testing_for_CSV_Injection", "Pruebas de Inyección CSV")</f>
+        <v/>
+      </c>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="n"/>
+    </row>
+    <row r="96" ht="16.5" customHeight="1" s="82">
+      <c r="A96" s="19" t="n"/>
+      <c r="B96" s="34" t="inlineStr">
+        <is>
+          <t>WSTG-INPV-22</t>
+        </is>
+      </c>
+      <c r="C96" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/22-Testing_for_Prototype_Pollution", "Pruebas de Prototype Pollution")</f>
+        <v/>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="82">
+      <c r="A97" s="97" t="n"/>
+      <c r="B97" s="98" t="n"/>
+      <c r="C97" s="99" t="n"/>
+      <c r="D97" s="99" t="n"/>
+      <c r="E97" s="99" t="n"/>
+      <c r="F97" s="99" t="n"/>
+    </row>
+    <row r="98" ht="47.25" customHeight="1" s="82">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="100" t="inlineStr">
         <is>
           <t>Testing for Error Handling</t>
         </is>
       </c>
-      <c r="C96" s="101" t="inlineStr">
+      <c r="C98" s="101" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D96" s="101" t="inlineStr">
+      <c r="D98" s="101" t="inlineStr">
         <is>
           <t>Objectives</t>
         </is>
       </c>
-      <c r="E96" s="101" t="inlineStr">
+      <c r="E98" s="101" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F96" s="101" t="inlineStr">
+      <c r="F98" s="101" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="33" customHeight="1" s="82">
-      <c r="A97" s="19" t="n"/>
-      <c r="B97" s="34" t="inlineStr">
+    <row r="99" ht="16.5" customHeight="1" s="82">
+      <c r="A99" s="19" t="n"/>
+      <c r="B99" s="34" t="inlineStr">
         <is>
           <t>WSTG-ERRH-01</t>
         </is>
       </c>
-      <c r="C97" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/08-Testing_for_Error_Handling/01-Testing_For_Improper_Error_Handling", "Testing for Improper Error Handling")</f>
-        <v/>
-      </c>
-      <c r="D97" s="16" t="inlineStr">
-        <is>
-          <t>- Identify existing error output.
-- Analyze the different output returned.</t>
-        </is>
-      </c>
-      <c r="E97" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F97" s="18" t="n"/>
-    </row>
-    <row r="98" ht="16.5" customHeight="1" s="82">
-      <c r="A98" s="19" t="n"/>
-      <c r="B98" s="34" t="inlineStr">
+      <c r="C99" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/08-Testing_for_Error_Handling/01-Testing_For_Improper_Error_Handling", "Pruebas de Manejo Improper de Errores")</f>
+        <v/>
+      </c>
+      <c r="D99" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F99" s="18" t="n"/>
+    </row>
+    <row r="100" ht="16.5" customHeight="1" s="82">
+      <c r="A100" s="19" t="n"/>
+      <c r="B100" s="34" t="inlineStr">
         <is>
           <t>WSTG-ERRH-02</t>
         </is>
       </c>
-      <c r="C98" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/08-Testing_for_Error_Handling/02-Testing_for_Stack_Traces", "Testing for Stack Traces")</f>
-        <v/>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E98" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F98" s="18" t="n"/>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="82">
-      <c r="A99" s="97" t="n"/>
-      <c r="B99" s="98" t="n"/>
-      <c r="C99" s="99" t="n"/>
-      <c r="D99" s="99" t="n"/>
-      <c r="E99" s="99" t="n"/>
-      <c r="F99" s="99" t="n"/>
-    </row>
-    <row r="100" ht="47.25" customHeight="1" s="82">
-      <c r="A100" s="9" t="n"/>
-      <c r="B100" s="100" t="inlineStr">
+      <c r="C100" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/08-Testing_for_Error_Handling/02-Testing_for_Stack_Traces", "Pruebas de Trazas de Pila (Stack Traces)")</f>
+        <v/>
+      </c>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="82">
+      <c r="A101" s="97" t="n"/>
+      <c r="B101" s="98" t="n"/>
+      <c r="C101" s="99" t="n"/>
+      <c r="D101" s="99" t="n"/>
+      <c r="E101" s="99" t="n"/>
+      <c r="F101" s="99" t="n"/>
+    </row>
+    <row r="102" ht="47.25" customHeight="1" s="82">
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="100" t="inlineStr">
         <is>
           <t>Testing for Weak Cryptography</t>
         </is>
       </c>
-      <c r="C100" s="101" t="inlineStr">
+      <c r="C102" s="101" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D100" s="101" t="inlineStr">
+      <c r="D102" s="101" t="inlineStr">
         <is>
           <t>Objectives</t>
         </is>
       </c>
-      <c r="E100" s="101" t="inlineStr">
+      <c r="E102" s="101" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F100" s="101" t="inlineStr">
+      <c r="F102" s="101" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="82.5" customHeight="1" s="82">
-      <c r="A101" s="19" t="n"/>
-      <c r="B101" s="34" t="inlineStr">
-        <is>
-          <t>WSTG-CRYP-01</t>
-        </is>
-      </c>
-      <c r="C101" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/09-Testing_for_Weak_Cryptography/01-Testing_for_Weak_Transport_Layer_Security", "Testing for Weak Transport Layer Security")</f>
-        <v/>
-      </c>
-      <c r="D101" s="16" t="inlineStr">
-        <is>
-          <t>- Validate the service configuration.
-- Review the digital certificate's cryptographic strength and validity.
-- Ensure that the TLS security is not bypassable and is properly implemented across the application.</t>
-        </is>
-      </c>
-      <c r="E101" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F101" s="18" t="n"/>
-    </row>
-    <row r="102" ht="49.5" customHeight="1" s="82">
-      <c r="A102" s="19" t="n"/>
-      <c r="B102" s="34" t="inlineStr">
-        <is>
-          <t>WSTG-CRYP-02</t>
-        </is>
-      </c>
-      <c r="C102" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/09-Testing_for_Weak_Cryptography/02-Testing_for_Padding_Oracle", "Testing for Padding Oracle")</f>
-        <v/>
-      </c>
-      <c r="D102" s="16" t="inlineStr">
-        <is>
-          <t>- Identify encrypted messages that rely on padding.
-- Attempt to break the padding of the encrypted messages and analyze the returned error messages for further analysis.</t>
-        </is>
-      </c>
-      <c r="E102" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F102" s="18" t="n"/>
-    </row>
-    <row r="103" ht="49.5" customHeight="1" s="82">
+    <row r="103" ht="33" customHeight="1" s="82">
       <c r="A103" s="19" t="n"/>
       <c r="B103" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CRYP-03</t>
+          <t>WSTG-CRYP-01</t>
         </is>
       </c>
       <c r="C103" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/09-Testing_for_Weak_Cryptography/03-Testing_for_Sensitive_Information_Sent_via_Unencrypted_Channels", "Testing for Sensitive Information Sent via Unencrypted Channels")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/09-Testing_for_Weak_Cryptography/01-Testing_for_Weak_Transport_Layer_Security", "Pruebas de Seguridad de Capa de Transporte Débil")</f>
         <v/>
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>- Identify sensitive information transmitted through the various channels.
-- Assess the privacy and security of the channels used.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr">
@@ -3775,131 +3730,125 @@
       </c>
       <c r="F103" s="18" t="n"/>
     </row>
-    <row r="104" ht="33" customHeight="1" s="82">
+    <row r="104" ht="16.5" customHeight="1" s="82">
       <c r="A104" s="19" t="n"/>
       <c r="B104" s="34" t="inlineStr">
         <is>
+          <t>WSTG-CRYP-02</t>
+        </is>
+      </c>
+      <c r="C104" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/09-Testing_for_Weak_Cryptography/02-Testing_for_Padding_Oracle", "Pruebas de Padding Oracle")</f>
+        <v/>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="n"/>
+    </row>
+    <row r="105" ht="33" customHeight="1" s="82">
+      <c r="A105" s="19" t="n"/>
+      <c r="B105" s="34" t="inlineStr">
+        <is>
+          <t>WSTG-CRYP-03</t>
+        </is>
+      </c>
+      <c r="C105" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/09-Testing_for_Weak_Cryptography/03-Testing_for_Sensitive_Information_Sent_via_Unencrypted_Channels", "Pruebas de Información Sensible Enviada vía Canales No Cifrados")</f>
+        <v/>
+      </c>
+      <c r="D105" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F105" s="18" t="n"/>
+    </row>
+    <row r="106" ht="33" customHeight="1" s="82">
+      <c r="A106" s="19" t="n"/>
+      <c r="B106" s="34" t="inlineStr">
+        <is>
           <t>WSTG-CRYP-04</t>
         </is>
       </c>
-      <c r="C104" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/09-Testing_for_Weak_Cryptography/04-Testing_for_Weak_Encryption", "Testing for Weak Encryption")</f>
-        <v/>
-      </c>
-      <c r="D104" s="16" t="inlineStr">
-        <is>
-          <t>- Provide a guideline for the identification weak encryption or hashing uses and implementations.</t>
-        </is>
-      </c>
-      <c r="E104" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F104" s="18" t="n"/>
-    </row>
-    <row r="105" ht="15" customHeight="1" s="82">
-      <c r="A105" s="97" t="n"/>
-      <c r="B105" s="98" t="n"/>
-      <c r="C105" s="99" t="n"/>
-      <c r="D105" s="99" t="n"/>
-      <c r="E105" s="99" t="n"/>
-      <c r="F105" s="99" t="n"/>
-    </row>
-    <row r="106" ht="47.25" customHeight="1" s="82">
-      <c r="A106" s="9" t="n"/>
-      <c r="B106" s="100" t="inlineStr">
+      <c r="C106" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/09-Testing_for_Weak_Cryptography/04-Testing_for_Weak_Cryptographic_Primitives", "Pruebas de Primitivas Criptográficas Débiles")</f>
+        <v/>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F106" s="18" t="n"/>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="82">
+      <c r="A107" s="97" t="n"/>
+      <c r="B107" s="98" t="n"/>
+      <c r="C107" s="99" t="n"/>
+      <c r="D107" s="99" t="n"/>
+      <c r="E107" s="99" t="n"/>
+      <c r="F107" s="99" t="n"/>
+    </row>
+    <row r="108" ht="47.25" customHeight="1" s="82">
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="100" t="inlineStr">
         <is>
           <t>Business Logic Testing</t>
         </is>
       </c>
-      <c r="C106" s="101" t="inlineStr">
+      <c r="C108" s="101" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D106" s="101" t="inlineStr">
+      <c r="D108" s="101" t="inlineStr">
         <is>
           <t>Objectives</t>
         </is>
       </c>
-      <c r="E106" s="101" t="inlineStr">
+      <c r="E108" s="101" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F106" s="101" t="inlineStr">
+      <c r="F108" s="101" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="82.5" customHeight="1" s="82">
-      <c r="A107" s="19" t="n"/>
-      <c r="B107" s="34" t="inlineStr">
-        <is>
-          <t>WSTG-BUSL-01</t>
-        </is>
-      </c>
-      <c r="C107" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/01-Test_Business_Logic_Data_Validation", "Test Business Logic Data Validation")</f>
-        <v/>
-      </c>
-      <c r="D107" s="16" t="inlineStr">
-        <is>
-          <t>- Identify data injection points.
-- Validate that all checks are occurring on the backend and can't be bypassed.
-- Attempt to break the format of the expected data and analyze how the application is handling it.</t>
-        </is>
-      </c>
-      <c r="E107" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F107" s="18" t="n"/>
-    </row>
-    <row r="108" ht="66" customHeight="1" s="82">
-      <c r="A108" s="19" t="n"/>
-      <c r="B108" s="34" t="inlineStr">
-        <is>
-          <t>WSTG-BUSL-02</t>
-        </is>
-      </c>
-      <c r="C108" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/02-Test_Ability_to_Forge_Requests", "Test Ability to Forge Requests")</f>
-        <v/>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>- Review the project documentation looking for guessable, predictable, or hidden functionality of fields.
-- Insert logically valid data in order to bypass normal business logic workflow.</t>
-        </is>
-      </c>
-      <c r="E108" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F108" s="18" t="n"/>
-    </row>
-    <row r="109" ht="148.5" customHeight="1" s="82">
+    <row r="109" ht="33" customHeight="1" s="82">
       <c r="A109" s="19" t="n"/>
       <c r="B109" s="34" t="inlineStr">
         <is>
-          <t>WSTG-BUSL-03</t>
+          <t>WSTG-BUSL-01</t>
         </is>
       </c>
       <c r="C109" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/03-Test_Integrity_Checks", "Test Integrity Checks")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/01-Test_Business_Logic_Data_Validation", "Probar la Validación de Datos de Lógica de Negocio")</f>
         <v/>
       </c>
       <c r="D109" s="16" t="inlineStr">
         <is>
-          <t>- Review the project documentation for components of the system that move, store, or handle data.
-- Determine what type of data is logically acceptable by the component and what types the system should guard against.
-- Determine who should be allowed to modify or read that data in each component.
-- Attempt to insert, update, or delete data values used by each component that should not be allowed per the business logic workflow.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr">
@@ -3909,21 +3858,20 @@
       </c>
       <c r="F109" s="18" t="n"/>
     </row>
-    <row r="110" ht="49.5" customHeight="1" s="82">
+    <row r="110" ht="33" customHeight="1" s="82">
       <c r="A110" s="19" t="n"/>
       <c r="B110" s="34" t="inlineStr">
         <is>
-          <t>WSTG-BUSL-04</t>
+          <t>WSTG-BUSL-02</t>
         </is>
       </c>
       <c r="C110" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/04-Test_for_Process_Timing", "Test for Process Timing")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/02-Test_Ability_to_Forge_Requests", "Probar la Capacidad de Falsificar Solicitudes")</f>
         <v/>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>- Review the project documentation for system functionality that may be impacted by time.
-- Develop and execute misuse cases.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E110" s="18" t="inlineStr">
@@ -3933,21 +3881,20 @@
       </c>
       <c r="F110" s="18" t="n"/>
     </row>
-    <row r="111" ht="66" customHeight="1" s="82">
+    <row r="111" ht="16.5" customHeight="1" s="82">
       <c r="A111" s="19" t="n"/>
       <c r="B111" s="34" t="inlineStr">
         <is>
-          <t>WSTG-BUSL-05</t>
+          <t>WSTG-BUSL-03</t>
         </is>
       </c>
       <c r="C111" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/05-Test_Number_of_Times_a_Function_Can_Be_Used_Limits", "Test Number of Times a Function Can Be Used Limits")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/03-Test_Integrity_Checks", "Probar Verificaciones de Integridad")</f>
         <v/>
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
-          <t>- Identify functions that must set limits to the times they can be called.
-- Assess if there is a logical limit set on the functions and if it is properly validated.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr">
@@ -3957,21 +3904,20 @@
       </c>
       <c r="F111" s="18" t="n"/>
     </row>
-    <row r="112" ht="82.5" customHeight="1" s="82">
+    <row r="112" ht="16.5" customHeight="1" s="82">
       <c r="A112" s="19" t="n"/>
       <c r="B112" s="34" t="inlineStr">
         <is>
-          <t>WSTG-BUSL-06</t>
+          <t>WSTG-BUSL-04</t>
         </is>
       </c>
       <c r="C112" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/06-Testing_for_the_Circumvention_of_Work_Flows", "Testing for the Circumvention of Work Flows")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/04-Test_for_Process_Timing", "Probar el Tiempo del Proceso")</f>
         <v/>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>- Review the project documentation for methods to skip or go through steps in the application process in a different order from the intended business logic flow.
-- Develop a misuse case and try to circumvent every logic flow identified.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E112" s="18" t="inlineStr">
@@ -3981,22 +3927,20 @@
       </c>
       <c r="F112" s="18" t="n"/>
     </row>
-    <row r="113" ht="99" customHeight="1" s="82">
+    <row r="113" ht="33" customHeight="1" s="82">
       <c r="A113" s="19" t="n"/>
       <c r="B113" s="34" t="inlineStr">
         <is>
-          <t>WSTG-BUSL-07</t>
+          <t>WSTG-BUSL-05</t>
         </is>
       </c>
       <c r="C113" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/07-Test_Defenses_Against_Application_Misuse", "Test Defenses Against Application Misuse")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/05-Test_Number_of_Times_a_Function_Can_Be_Used_Limits", "Probar Límites en el Número de Veces que una Función Puede Ser Usada")</f>
         <v/>
       </c>
       <c r="D113" s="16" t="inlineStr">
         <is>
-          <t>- Generate notes from all tests conducted against the system.
-- Review which tests had a different functionality based on aggressive input.
-- Understand the defenses in place and verify if they are enough to protect the system against bypassing techniques.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E113" s="18" t="inlineStr">
@@ -4006,22 +3950,20 @@
       </c>
       <c r="F113" s="18" t="n"/>
     </row>
-    <row r="114" ht="99" customHeight="1" s="82">
+    <row r="114" ht="16.5" customHeight="1" s="82">
       <c r="A114" s="19" t="n"/>
       <c r="B114" s="34" t="inlineStr">
         <is>
-          <t>WSTG-BUSL-08</t>
+          <t>WSTG-BUSL-06</t>
         </is>
       </c>
       <c r="C114" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/08-Test_Upload_of_Unexpected_File_Types", "Test Upload of Unexpected File Types")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/06-Testing_for_the_Circumvention_of_Work_Flows", "Pruebas de Evasión de Flujos de Trabajo")</f>
         <v/>
       </c>
       <c r="D114" s="16" t="inlineStr">
         <is>
-          <t>- Review the project documentation for file types that are rejected by the system.
-- Verify that the unwelcomed file types are rejected and handled safely.
-- Verify that file batch uploads are secure and do not allow any bypass against the set security measures.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E114" s="18" t="inlineStr">
@@ -4031,25 +3973,20 @@
       </c>
       <c r="F114" s="18" t="n"/>
     </row>
-    <row r="115" ht="165" customHeight="1" s="82">
+    <row r="115" ht="33" customHeight="1" s="82">
       <c r="A115" s="19" t="n"/>
       <c r="B115" s="34" t="inlineStr">
         <is>
-          <t>WSTG-BUSL-09</t>
+          <t>WSTG-BUSL-07</t>
         </is>
       </c>
       <c r="C115" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/09-Test_Upload_of_Malicious_Files", "Test Upload of Malicious Files")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/07-Test_Defenses_Against_Application_Misuse", "Probar Defensas contra el Uso Indebido de la Aplicación")</f>
         <v/>
       </c>
       <c r="D115" s="16" t="inlineStr">
         <is>
-          <t>- Identify the file upload functionality.
-- Review the project documentation to identify what file types are considered acceptable, and what types would be considered dangerous or malicious.
-- If documentation is not available then consider what would be appropriate based on the purpose of the application.
-- Determine how the uploaded files are processed.
-- Obtain or create a set of malicious files for testing.
-- Try to upload the malicious files to the application and determine whether it is accepted and processed.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E115" s="18" t="inlineStr">
@@ -4059,128 +3996,125 @@
       </c>
       <c r="F115" s="18" t="n"/>
     </row>
-    <row r="116" ht="66" customHeight="1" s="82">
+    <row r="116" ht="33" customHeight="1" s="82">
       <c r="A116" s="19" t="n"/>
       <c r="B116" s="34" t="inlineStr">
         <is>
+          <t>WSTG-BUSL-08</t>
+        </is>
+      </c>
+      <c r="C116" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/08-Test_Upload_of_Unexpected_File_Types", "Probar la Subida de Tipos de Archivo Inesperados")</f>
+        <v/>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="n"/>
+    </row>
+    <row r="117" ht="16.5" customHeight="1" s="82">
+      <c r="A117" s="19" t="n"/>
+      <c r="B117" s="34" t="inlineStr">
+        <is>
+          <t>WSTG-BUSL-09</t>
+        </is>
+      </c>
+      <c r="C117" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/09-Test_Upload_of_Malicious_Files", "Probar la Subida de Archivos Maliciosos")</f>
+        <v/>
+      </c>
+      <c r="D117" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="n"/>
+    </row>
+    <row r="118" ht="16.5" customHeight="1" s="82">
+      <c r="A118" s="19" t="n"/>
+      <c r="B118" s="34" t="inlineStr">
+        <is>
           <t>WSTG-BUSL-10</t>
         </is>
       </c>
-      <c r="C116" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/10-Test-Payment-Functionality", "Test Payment Functionality")</f>
-        <v/>
-      </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>- Determine whether the business logic for the e-commerce functionality is robust.
-- Understand how the payment functionality works.
-- Determine whether the payment functionality is secure.</t>
-        </is>
-      </c>
-      <c r="E116" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F116" s="18" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1" s="82">
-      <c r="A117" s="97" t="n"/>
-      <c r="B117" s="98" t="n"/>
-      <c r="C117" s="99" t="n"/>
-      <c r="D117" s="99" t="n"/>
-      <c r="E117" s="99" t="n"/>
-      <c r="F117" s="99" t="n"/>
-    </row>
-    <row r="118" ht="47.25" customHeight="1" s="82">
-      <c r="A118" s="9" t="n"/>
-      <c r="B118" s="100" t="inlineStr">
+      <c r="C118" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/10-Business_Logic_Testing/10-Test-Payment-Functionality", "Probar la Funcionalidad de Pago")</f>
+        <v/>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="n"/>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="82">
+      <c r="A119" s="97" t="n"/>
+      <c r="B119" s="98" t="n"/>
+      <c r="C119" s="99" t="n"/>
+      <c r="D119" s="99" t="n"/>
+      <c r="E119" s="99" t="n"/>
+      <c r="F119" s="99" t="n"/>
+    </row>
+    <row r="120" ht="47.25" customHeight="1" s="82">
+      <c r="A120" s="9" t="n"/>
+      <c r="B120" s="100" t="inlineStr">
         <is>
           <t>Client-side Testing</t>
         </is>
       </c>
-      <c r="C118" s="101" t="inlineStr">
+      <c r="C120" s="101" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D118" s="101" t="inlineStr">
+      <c r="D120" s="101" t="inlineStr">
         <is>
           <t>Objectives</t>
         </is>
       </c>
-      <c r="E118" s="101" t="inlineStr">
+      <c r="E120" s="101" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F118" s="101" t="inlineStr">
+      <c r="F120" s="101" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="119" ht="33" customHeight="1" s="82">
-      <c r="A119" s="19" t="n"/>
-      <c r="B119" s="34" t="inlineStr">
-        <is>
-          <t>WSTG-CLNT-01</t>
-        </is>
-      </c>
-      <c r="C119" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/01-Testing_for_DOM-based_Cross_Site_Scripting", "Testing for DOM-Based Cross Site Scripting")</f>
-        <v/>
-      </c>
-      <c r="D119" s="16" t="inlineStr">
-        <is>
-          <t>- Identify DOM sinks.
-- Build payloads that pertain to every sink type.</t>
-        </is>
-      </c>
-      <c r="E119" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F119" s="18" t="n"/>
-    </row>
-    <row r="120" ht="16.5" customHeight="1" s="82">
-      <c r="A120" s="19" t="n"/>
-      <c r="B120" s="34" t="inlineStr">
-        <is>
-          <t>WSTG-CLNT-02</t>
-        </is>
-      </c>
-      <c r="C120" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/02-Testing_for_JavaScript_Execution", "Testing for JavaScript Execution")</f>
-        <v/>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>- Identify sinks and possible JavaScript injection points.</t>
-        </is>
-      </c>
-      <c r="E120" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F120" s="18" t="n"/>
     </row>
     <row r="121" ht="33" customHeight="1" s="82">
       <c r="A121" s="19" t="n"/>
       <c r="B121" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-03</t>
+          <t>WSTG-CLNT-01</t>
         </is>
       </c>
       <c r="C121" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/03-Testing_for_HTML_Injection", "Testing for HTML Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/01-Testing_for_DOM-based_Cross_Site_Scripting", "Pruebas de Cross Site Scripting Basado en DOM")</f>
         <v/>
       </c>
       <c r="D121" s="16" t="inlineStr">
         <is>
-          <t>- Identify HTML injection points and assess the severity of the injected content.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E121" s="18" t="inlineStr">
@@ -4190,21 +4124,20 @@
       </c>
       <c r="F121" s="18" t="n"/>
     </row>
-    <row r="122" ht="33" customHeight="1" s="82">
+    <row r="122" ht="16.5" customHeight="1" s="82">
       <c r="A122" s="19" t="n"/>
       <c r="B122" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-04</t>
+          <t>WSTG-CLNT-02</t>
         </is>
       </c>
       <c r="C122" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/04-Testing_for_Client-side_URL_Redirect", "Testing for Client-side URL Redirect")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/02-Testing_for_JavaScript_Execution", "Pruebas de Ejecución de JavaScript")</f>
         <v/>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>- Identify injection points that handle URLs or paths.
-- Assess the locations that the system could redirect to.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E122" s="18" t="inlineStr">
@@ -4214,21 +4147,20 @@
       </c>
       <c r="F122" s="18" t="n"/>
     </row>
-    <row r="123" ht="33" customHeight="1" s="82">
+    <row r="123" ht="16.5" customHeight="1" s="82">
       <c r="A123" s="19" t="n"/>
       <c r="B123" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-05</t>
+          <t>WSTG-CLNT-03</t>
         </is>
       </c>
       <c r="C123" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/05-Testing_for_CSS_Injection", "Testing for CSS Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/03-Testing_for_HTML_Injection", "Pruebas de Inyección HTML")</f>
         <v/>
       </c>
       <c r="D123" s="16" t="inlineStr">
         <is>
-          <t>- Identify CSS injection points.
-- Assess the impact of the injection.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E123" s="18" t="inlineStr">
@@ -4242,17 +4174,16 @@
       <c r="A124" s="19" t="n"/>
       <c r="B124" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-06</t>
+          <t>WSTG-CLNT-04</t>
         </is>
       </c>
       <c r="C124" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/06-Testing_for_Client-side_Resource_Manipulation", "Testing for Client-side Resource Manipulation")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/04-Testing_for_Client-side_URL_Redirect", "Pruebas de Redirección de URL del Lado del Cliente")</f>
         <v/>
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>- Identify sinks with weak input validation.
-- Assess the impact of the resource manipulation.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E124" s="18" t="inlineStr">
@@ -4262,21 +4193,20 @@
       </c>
       <c r="F124" s="18" t="n"/>
     </row>
-    <row r="125" ht="33" customHeight="1" s="82">
+    <row r="125" ht="16.5" customHeight="1" s="82">
       <c r="A125" s="19" t="n"/>
       <c r="B125" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-07</t>
+          <t>WSTG-CLNT-05</t>
         </is>
       </c>
       <c r="C125" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/07-Testing_Cross_Origin_Resource_Sharing", "Testing Cross Origin Resource Sharing")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/05-Testing_for_CSS_Injection", "Pruebas de Inyección CSS")</f>
         <v/>
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>- Identify endpoints that implement CORS.
-- Ensure that the CORS configuration is secure or harmless.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E125" s="18" t="inlineStr">
@@ -4290,17 +4220,16 @@
       <c r="A126" s="19" t="n"/>
       <c r="B126" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-08</t>
+          <t>WSTG-CLNT-06</t>
         </is>
       </c>
       <c r="C126" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/08-Testing_for_Cross_Site_Flashing", "Testing for Cross Site Flashing")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/06-Testing_for_Client-side_Resource_Manipulation", "Pruebas de Manipulación de Recursos del Lado del Cliente")</f>
         <v/>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>- Decompile and analyze the application's code.
-- Assess sinks inputs and unsafe method usages.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E126" s="18" t="inlineStr">
@@ -4314,16 +4243,16 @@
       <c r="A127" s="19" t="n"/>
       <c r="B127" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-09</t>
+          <t>WSTG-CLNT-07</t>
         </is>
       </c>
       <c r="C127" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/09-Testing_for_Clickjacking", "Testing for Clickjacking")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/07-Testing_Cross_Origin_Resource_Sharing", "Pruebas de Cross Origin Resource Sharing")</f>
         <v/>
       </c>
       <c r="D127" s="16" t="inlineStr">
         <is>
-          <t>- Assess application vulnerability to clickjacking attacks.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E127" s="18" t="inlineStr">
@@ -4333,21 +4262,20 @@
       </c>
       <c r="F127" s="18" t="n"/>
     </row>
-    <row r="128" ht="49.5" customHeight="1" s="82">
+    <row r="128" ht="16.5" customHeight="1" s="82">
       <c r="A128" s="19" t="n"/>
       <c r="B128" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-10</t>
+          <t>WSTG-CLNT-08</t>
         </is>
       </c>
       <c r="C128" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/10-Testing_WebSockets", "Testing WebSockets")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/08-Testing_for_Cross_Site_Flashing", "Pruebas de Cross Site Flashing")</f>
         <v/>
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>- Identify the usage of WebSockets.
-- Assess its implementation by using the same tests on normal HTTP channels.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E128" s="18" t="inlineStr">
@@ -4357,21 +4285,20 @@
       </c>
       <c r="F128" s="18" t="n"/>
     </row>
-    <row r="129" ht="49.5" customHeight="1" s="82">
+    <row r="129" ht="16.5" customHeight="1" s="82">
       <c r="A129" s="19" t="n"/>
       <c r="B129" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-11</t>
+          <t>WSTG-CLNT-09</t>
         </is>
       </c>
       <c r="C129" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/11-Testing_Web_Messaging", "Testing Web Messaging")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/09-Testing_for_Clickjacking", "Pruebas de Clickjacking")</f>
         <v/>
       </c>
       <c r="D129" s="16" t="inlineStr">
         <is>
-          <t>- Assess the security of the message's origin.
-- Validate that it's using safe methods and validating its input.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E129" s="18" t="inlineStr">
@@ -4381,21 +4308,20 @@
       </c>
       <c r="F129" s="18" t="n"/>
     </row>
-    <row r="130" ht="82.5" customHeight="1" s="82">
+    <row r="130" ht="16.5" customHeight="1" s="82">
       <c r="A130" s="19" t="n"/>
       <c r="B130" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-12</t>
+          <t>WSTG-CLNT-10</t>
         </is>
       </c>
       <c r="C130" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/12-Testing_Browser_Storage", "Testing Browser Storage")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/10-Testing_WebSockets", "Pruebas de WebSockets")</f>
         <v/>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>- Determine whether the website is storing sensitive data in client-side storage.
-- The code handling of the storage objects should be examined for possibilities of injection attacks, such as utilizing unvalidated input or vulnerable libraries.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E130" s="18" t="inlineStr">
@@ -4405,21 +4331,20 @@
       </c>
       <c r="F130" s="18" t="n"/>
     </row>
-    <row r="131" ht="49.5" customHeight="1" s="82">
+    <row r="131" ht="16.5" customHeight="1" s="82">
       <c r="A131" s="19" t="n"/>
       <c r="B131" s="34" t="inlineStr">
         <is>
-          <t>WSTG-CLNT-13</t>
+          <t>WSTG-CLNT-11</t>
         </is>
       </c>
       <c r="C131" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/13-Testing_for_Cross_Site_Script_Inclusion", "Testing for Cross Site Script Inclusion")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/11-Testing_Web_Messaging", "Pruebas de Web Messaging")</f>
         <v/>
       </c>
       <c r="D131" s="16" t="inlineStr">
         <is>
-          <t>- Locate sensitive data across the system.
-- Assess the leakage of sensitive data through various techniques.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E131" s="18" t="inlineStr">
@@ -4433,141 +4358,252 @@
       <c r="A132" s="19" t="n"/>
       <c r="B132" s="34" t="inlineStr">
         <is>
+          <t>WSTG-CLNT-12</t>
+        </is>
+      </c>
+      <c r="C132" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/12-Testing_Browser_Storage", "Pruebas de Almacenamiento del Navegador")</f>
+        <v/>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="n"/>
+    </row>
+    <row r="133" ht="16.5" customHeight="1" s="82">
+      <c r="A133" s="19" t="n"/>
+      <c r="B133" s="34" t="inlineStr">
+        <is>
+          <t>WSTG-CLNT-13</t>
+        </is>
+      </c>
+      <c r="C133" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/13-Testing_for_Cross_Site_Script_Inclusion", "Pruebas de Cross Site Script Inclusion")</f>
+        <v/>
+      </c>
+      <c r="D133" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E133" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F133" s="18" t="n"/>
+    </row>
+    <row r="134" ht="16.5" customHeight="1" s="82">
+      <c r="A134" s="19" t="n"/>
+      <c r="B134" s="34" t="inlineStr">
+        <is>
           <t>WSTG-CLNT-14</t>
         </is>
       </c>
-      <c r="C132" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/14-Testing_for_Reverse_Tabnabbing", "Testing for Reverse Tabnabbing")</f>
-        <v/>
-      </c>
-      <c r="D132" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E132" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F132" s="18" t="n"/>
-    </row>
-    <row r="133" ht="15" customHeight="1" s="82">
-      <c r="A133" s="97" t="n"/>
-      <c r="B133" s="98" t="n"/>
-      <c r="C133" s="99" t="n"/>
-      <c r="D133" s="99" t="n"/>
-      <c r="E133" s="99" t="n"/>
-      <c r="F133" s="99" t="n"/>
-    </row>
-    <row r="134" ht="47.25" customHeight="1" s="82">
-      <c r="A134" s="9" t="n"/>
-      <c r="B134" s="100" t="inlineStr">
-        <is>
-          <t>API Testing</t>
-        </is>
-      </c>
-      <c r="C134" s="101" t="inlineStr">
-        <is>
-          <t>Test Name</t>
-        </is>
-      </c>
-      <c r="D134" s="101" t="inlineStr">
-        <is>
-          <t>Objectives</t>
-        </is>
-      </c>
-      <c r="E134" s="101" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F134" s="101" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="99" customHeight="1" s="82">
+      <c r="C134" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/14-Testing_for_Reverse_Tabnabbing", "Pruebas de Reverse Tabnabbing")</f>
+        <v/>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="n"/>
+    </row>
+    <row r="135" ht="33" customHeight="1" s="82">
       <c r="A135" s="19" t="n"/>
       <c r="B135" s="34" t="inlineStr">
         <is>
+          <t>WSTG-CLNT-15</t>
+        </is>
+      </c>
+      <c r="C135" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/11-Client-side_Testing/15-Testing_for_Client-Side_Template_Injection", "Pruebas de Inyección de Plantillas del Lado del Cliente")</f>
+        <v/>
+      </c>
+      <c r="D135" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="n"/>
+    </row>
+    <row r="136" ht="15" customHeight="1" s="82">
+      <c r="A136" s="97" t="n"/>
+      <c r="B136" s="98" t="n"/>
+      <c r="C136" s="99" t="n"/>
+      <c r="D136" s="99" t="n"/>
+      <c r="E136" s="99" t="n"/>
+      <c r="F136" s="99" t="n"/>
+    </row>
+    <row r="137" ht="47.25" customHeight="1" s="82">
+      <c r="A137" s="9" t="n"/>
+      <c r="B137" s="100" t="inlineStr">
+        <is>
+          <t>API Testing</t>
+        </is>
+      </c>
+      <c r="C137" s="101" t="inlineStr">
+        <is>
+          <t>Test Name</t>
+        </is>
+      </c>
+      <c r="D137" s="101" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="E137" s="101" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F137" s="101" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="16.5" customHeight="1" s="82">
+      <c r="A138" s="19" t="n"/>
+      <c r="B138" s="34" t="inlineStr">
+        <is>
           <t>WSTG-APIT-01</t>
         </is>
       </c>
-      <c r="C135" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/12-API_Testing/01-API_Reconnaissance", "API Reconnaissance")</f>
-        <v/>
-      </c>
-      <c r="D135" s="16" t="inlineStr">
-        <is>
-          <t>- Find all API endpoints supported by the backend server code, documented or undocumented.
-- Find all parameters for each endpoint supported by the backend server, documented or undocumented.
-- Discover interesting data related to APIs in HTML and JavaScript sent to clients.</t>
-        </is>
-      </c>
-      <c r="E135" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F135" s="18" t="n"/>
-    </row>
-    <row r="136" ht="66" customHeight="1" s="82">
-      <c r="A136" s="19" t="n"/>
-      <c r="B136" s="34" t="inlineStr">
+      <c r="C138" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/12-API_Testing/01-API_Reconnaissance", "Reconocimiento de API")</f>
+        <v/>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="n"/>
+    </row>
+    <row r="139" ht="33" customHeight="1" s="82">
+      <c r="A139" s="19" t="n"/>
+      <c r="B139" s="34" t="inlineStr">
         <is>
           <t>WSTG-APIT-02</t>
         </is>
       </c>
-      <c r="C136" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/12-API_Testing/02-API_Broken_Object_Level_Authorization", "API Broken Object Level Authorization")</f>
-        <v/>
-      </c>
-      <c r="D136" s="16" t="inlineStr">
-        <is>
-          <t>- The objective of this test is to identify whether the API enforces proper **object-level authorization** checks, ensuring that users can only access and manipulate objects they are authorized to interact with.</t>
-        </is>
-      </c>
-      <c r="E136" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F136" s="18" t="n"/>
-    </row>
-    <row r="137" ht="66" customHeight="1" s="82">
-      <c r="A137" s="19" t="n"/>
-      <c r="B137" s="34" t="inlineStr">
+      <c r="C139" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/12-API_Testing/02-API_Broken_Object_Level_Authorization", "Autorización Rota a Nivel de Objeto de API")</f>
+        <v/>
+      </c>
+      <c r="D139" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E139" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F139" s="18" t="n"/>
+    </row>
+    <row r="140" ht="16.5" customHeight="1" s="82">
+      <c r="A140" s="19" t="n"/>
+      <c r="B140" s="34" t="inlineStr">
+        <is>
+          <t>WSTG-APIT-03</t>
+        </is>
+      </c>
+      <c r="C140" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/12-API_Testing/03-Testing_for_Excessive_Data_Exposure", "Pruebas de Exposición Excesiva de Datos")</f>
+        <v/>
+      </c>
+      <c r="D140" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="n"/>
+    </row>
+    <row r="141" ht="33" customHeight="1" s="82">
+      <c r="A141" s="19" t="n"/>
+      <c r="B141" s="34" t="inlineStr">
+        <is>
+          <t>WSTG-APIT-04</t>
+        </is>
+      </c>
+      <c r="C141" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/12-API_Testing/04-API_Broken_Function_Level_Authorization", "Autorización Rota a Nivel de Función de API")</f>
+        <v/>
+      </c>
+      <c r="D141" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E141" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="n"/>
+    </row>
+    <row r="142" ht="16.5" customHeight="1" s="82">
+      <c r="A142" s="19" t="n"/>
+      <c r="B142" s="34" t="inlineStr">
         <is>
           <t>WSTG-APIT-99</t>
         </is>
       </c>
-      <c r="C137" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/12-API_Testing/99-Testing_GraphQL", "Testing GraphQL")</f>
-        <v/>
-      </c>
-      <c r="D137" s="16" t="inlineStr">
-        <is>
-          <t>- Assess that a secure and production-ready configuration is deployed.
-- Validate all input fields against generic attacks.
-- Ensure that proper access controls are applied.</t>
-        </is>
-      </c>
-      <c r="E137" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F137" s="18" t="n"/>
-    </row>
-    <row r="138" ht="15" customHeight="1" s="82">
-      <c r="A138" s="97" t="n"/>
-      <c r="B138" s="98" t="n"/>
-      <c r="C138" s="99" t="n"/>
-      <c r="D138" s="99" t="n"/>
-      <c r="E138" s="99" t="n"/>
-      <c r="F138" s="99" t="n"/>
+      <c r="C142" s="15">
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/12-API_Testing/99-Testing_GraphQL", "Pruebas de GraphQL")</f>
+        <v/>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="n"/>
+    </row>
+    <row r="143" ht="15" customHeight="1" s="82">
+      <c r="A143" s="97" t="n"/>
+      <c r="B143" s="98" t="n"/>
+      <c r="C143" s="99" t="n"/>
+      <c r="D143" s="99" t="n"/>
+      <c r="E143" s="99" t="n"/>
+      <c r="F143" s="99" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4584,7 +4620,7 @@
       <formula>$E4="Issues"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:F138">
+  <conditionalFormatting sqref="B4:F143">
     <cfRule type="expression" priority="1" dxfId="13">
       <formula>$E4="Pass"</formula>
     </cfRule>
@@ -4596,7 +4632,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E34 E35 E36 E37 E38 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E54 E55 E56 E57 E58 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E97 E98 E101 E102 E103 E104 E107 E108 E109 E110 E111 E112 E113 E114 E115 E116 E119 E120 E121 E122 E123 E124 E125 E126 E127 E128 E129 E130 E131 E132 E135 E136 E137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E34 E35 E36 E37 E38 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E54 E55 E56 E57 E58 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E95 E96 E99 E100 E103 E104 E105 E106 E109 E110 E111 E112 E113 E114 E115 E116 E117 E118 E121 E122 E123 E124 E125 E126 E127 E128 E129 E130 E131 E132 E133 E134 E135 E138 E139 E140 E141 E142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,Pass,Issues,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/checklists/checklist.xlsx
+++ b/checklists/checklist.xlsx
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F26" s="18" t="n"/>
     </row>
-    <row r="27" ht="33" customHeight="1" s="82">
+    <row r="27" ht="16.5" customHeight="1" s="82">
       <c r="A27" s="19" t="n"/>
       <c r="B27" s="34" t="inlineStr">
         <is>
@@ -2024,13 +2024,12 @@
         </is>
       </c>
       <c r="C27" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/10-Test_for_Subdomain_Takeover", "Test for Subdomain Takeover")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/10-Test_for_Subdomain_Takeover", "Probar Subdomain Takeover")</f>
         <v/>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>- Enumerate all possible domains (previous and current).
-- Identify any forgotten or misconfigured domains.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
@@ -2040,7 +2039,7 @@
       </c>
       <c r="F27" s="18" t="n"/>
     </row>
-    <row r="28" ht="33" customHeight="1" s="82">
+    <row r="28" ht="16.5" customHeight="1" s="82">
       <c r="A28" s="19" t="n"/>
       <c r="B28" s="34" t="inlineStr">
         <is>
@@ -2048,12 +2047,12 @@
         </is>
       </c>
       <c r="C28" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/11-Test_Cloud_Storage", "Test Cloud Storage")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/11-Test_Cloud_Storage", "Probar Almacenamiento en la Nube")</f>
         <v/>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>- Assess that the access control configuration for the storage services is properly in place.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
@@ -2063,7 +2062,7 @@
       </c>
       <c r="F28" s="18" t="n"/>
     </row>
-    <row r="29" ht="33" customHeight="1" s="82">
+    <row r="29" ht="16.5" customHeight="1" s="82">
       <c r="A29" s="19" t="n"/>
       <c r="B29" s="34" t="inlineStr">
         <is>
@@ -2071,12 +2070,12 @@
         </is>
       </c>
       <c r="C29" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/12-Test_for_Content_Security_Policy", "Testing for Content Security Policy")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/12-Test_for_Content_Security_Policy", "Pruebas de Content Security Policy")</f>
         <v/>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>- Review the Content-Security-Policy header or meta element to identify misconfigurations.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">

--- a/checklists/checklist.xlsx
+++ b/checklists/checklist.xlsx
@@ -1609,7 +1609,7 @@
       </c>
       <c r="F8" s="18" t="n"/>
     </row>
-    <row r="9" ht="115.5" customHeight="1" s="82">
+    <row r="9" ht="16.5" customHeight="1" s="82">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="34" t="inlineStr">
         <is>
@@ -1617,15 +1617,12 @@
         </is>
       </c>
       <c r="C9" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/04-Attack_Surface_Identification", "Attack Surface Identification")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/01-Information_Gathering/04-Attack_Surface_Identification", "Identificación de Superficie de Ataque")</f>
         <v/>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>- Enumerate all web applications within scope.
-- Identify DNS names, domains, and virtual hosts associated with the target.
-- Discover additional domains and subdomains using passive and active DNS techniques.
-- Analyze digital certificates and Certificate Transparency logs for additional hostnames.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -2108,7 +2105,7 @@
       </c>
       <c r="F30" s="18" t="n"/>
     </row>
-    <row r="31" ht="66" customHeight="1" s="82">
+    <row r="31" ht="33" customHeight="1" s="82">
       <c r="A31" s="19" t="n"/>
       <c r="B31" s="34" t="inlineStr">
         <is>
@@ -2116,14 +2113,12 @@
         </is>
       </c>
       <c r="C31" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/14-Test_Other_HTTP_Security_Header_Misconfigurations", "Test Other HTTP Security Header Misconfigurations")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/02-Configuration_and_Deployment_Management_Testing/14-Test_Other_HTTP_Security_Header_Misconfigurations", "Probar Otras Mala Configuraciones de Encabezados de Seguridad HTTP")</f>
         <v/>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>- Identify improperly configured security headers.
-- Assess the impact of misconfigured security headers.
-- Validate the correct implementation of required security headers.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">

--- a/checklists/checklist.xlsx
+++ b/checklists/checklist.xlsx
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F36" s="18" t="n"/>
     </row>
-    <row r="37" ht="49.5" customHeight="1" s="82">
+    <row r="37" ht="33" customHeight="1" s="82">
       <c r="A37" s="19" t="n"/>
       <c r="B37" s="34" t="inlineStr">
         <is>
@@ -2241,13 +2241,12 @@
         </is>
       </c>
       <c r="C37" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/04-Testing_for_Account_Enumeration_and_Guessable_User_Account", "Testing for Account Enumeration and Guessable User Account")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/03-Identity_Management_Testing/04-Testing_for_Account_Enumeration_and_Guessable_User_Account", "Pruebas de Enumeración de Cuentas y Cuenta de Usuario Adivinable")</f>
         <v/>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>- Review processes that pertain to user identification (*e.g.* registration, login, etc.).
-- Enumerate users where possible through response analysis.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr">
@@ -3393,7 +3392,7 @@
       </c>
       <c r="F88" s="18" t="n"/>
     </row>
-    <row r="89" ht="115.5" customHeight="1" s="82">
+    <row r="89" ht="16.5" customHeight="1" s="82">
       <c r="A89" s="19" t="n"/>
       <c r="B89" s="34" t="inlineStr">
         <is>
@@ -3401,14 +3400,12 @@
         </is>
       </c>
       <c r="C89" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/15-Testing_for_HTTP_Response_Splitting", "Testing for HTTP Response Splitting")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/15-Testing_for_HTTP_Response_Splitting", "Pruebas de HTTP Response Splitting")</f>
         <v/>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>- Identify user-controlled input that is reflected into HTTP response headers.
-- Assess whether CR (`\r`) and LF (`\n`) characters can be injected into response headers.
-- Determine the potential impact of successful HTTP Response Splitting attacks, such as cache poisoning or client-side exploitation.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr">
@@ -3418,7 +3415,7 @@
       </c>
       <c r="F89" s="18" t="n"/>
     </row>
-    <row r="90" ht="99" customHeight="1" s="82">
+    <row r="90" ht="16.5" customHeight="1" s="82">
       <c r="A90" s="19" t="n"/>
       <c r="B90" s="34" t="inlineStr">
         <is>
@@ -3426,16 +3423,12 @@
         </is>
       </c>
       <c r="C90" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/16-Testing_for_HTTP_Request_Smuggling", "Testing for HTTP Request Smuggling")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/16-Testing_for_HTTP_Request_Smuggling", "Pruebas de HTTP Request Smuggling")</f>
         <v/>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>- Identify request boundary inconsistencies between frontend and backend components
-- Detect classic CL/TE desynchronization vulnerabilities
-- Evaluate protocol translation logic (HTTP/2 → HTTP/1.1)
-- Assess H2C upgrade handling and downgrade safety
-- Confirm backend request queue poisoning</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E90" s="18" t="inlineStr">

--- a/checklists/checklist.xlsx
+++ b/checklists/checklist.xlsx
@@ -2698,7 +2698,7 @@
       </c>
       <c r="F57" s="18" t="n"/>
     </row>
-    <row r="58" ht="33" customHeight="1" s="82">
+    <row r="58" ht="16.5" customHeight="1" s="82">
       <c r="A58" s="19" t="n"/>
       <c r="B58" s="34" t="inlineStr">
         <is>
@@ -2706,12 +2706,12 @@
         </is>
       </c>
       <c r="C58" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/05-Testing_for_OAuth_Weaknesses", "Testing for OAuth Weaknesses")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/05-Authorization_Testing/05-Testing_for_OAuth_Weaknesses", "Pruebas de Debilidades de OAuth")</f>
         <v/>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>- Determine if OAuth2 implementation is vulnerable or using a deprecated or custom implementation.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E58" s="18" t="inlineStr">

--- a/checklists/checklist.xlsx
+++ b/checklists/checklist.xlsx
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>- Validar que la sesión generada se gestione de manera segura y no ponga en peligro las credenciales del usuario.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F45" s="18" t="n"/>
     </row>
-    <row r="46" ht="49.5" customHeight="1" s="82">
+    <row r="46" ht="33" customHeight="1" s="82">
       <c r="A46" s="19" t="n"/>
       <c r="B46" s="34" t="inlineStr">
         <is>
@@ -2443,8 +2443,7 @@
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>- Revisar si la aplicación almacena información sensible en el lado del cliente.
-- Revisar si se puede acceder sin autorización.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
@@ -2674,7 +2673,7 @@
       </c>
       <c r="F56" s="18" t="n"/>
     </row>
-    <row r="57" ht="66" customHeight="1" s="82">
+    <row r="57" ht="33" customHeight="1" s="82">
       <c r="A57" s="19" t="n"/>
       <c r="B57" s="34" t="inlineStr">
         <is>
@@ -2687,8 +2686,7 @@
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>- Identificar puntos donde pueden ocurrir referencias a objetos.
-- Evaluar las medidas de control de acceso y si son vulnerables a IDOR.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr">
@@ -2862,7 +2860,7 @@
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>- Determinar si es posible iniciar solicitudes en nombre de un usuario que no son iniciadas por el usuario.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr">
@@ -3138,7 +3136,7 @@
       </c>
       <c r="F77" s="18" t="n"/>
     </row>
-    <row r="78" ht="49.5" customHeight="1" s="82">
+    <row r="78" ht="16.5" customHeight="1" s="82">
       <c r="A78" s="19" t="n"/>
       <c r="B78" s="34" t="inlineStr">
         <is>
@@ -3146,13 +3144,12 @@
         </is>
       </c>
       <c r="C78" s="15">
-        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/05-Testing_for_SQL_Injection", "Testing for SQL Injection")</f>
+        <f>HYPERLINK("https://owasp.org/www-project-web-security-testing-guide/latest/4-Web_Application_Security_Testing/07-Input_Validation_Testing/05-Testing_for_SQL_Injection", "Pruebas de Inyección SQL")</f>
         <v/>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>- Identificar puntos de inyección SQL.
-- Evaluar la gravedad de la inyección y el nivel de acceso que se puede lograr a través de ella.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E78" s="18" t="inlineStr">
